--- a/artfynd/A 13663-2023 artfynd.xlsx
+++ b/artfynd/A 13663-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13663-2023 artfynd.xlsx
+++ b/artfynd/A 13663-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111396053</v>
+        <v>111483140</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S om järnvägen - 2, Vg</t>
+          <t>S om järnvägen - 9, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432083.280685614</v>
+        <v>431943</v>
       </c>
       <c r="R2" t="n">
-        <v>6419676.539718015</v>
+        <v>6419626</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -760,19 +746,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +760,26 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -800,62 +796,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111396060</v>
+        <v>111483105</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S om järnvägen - 3, Vg</t>
+          <t>S om järnvägen - 8, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432076.641898193</v>
+        <v>431947</v>
       </c>
       <c r="R3" t="n">
-        <v>6419661.774153749</v>
+        <v>6419623</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,19 +867,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,6 +881,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -925,66 +917,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111396045</v>
+        <v>111483197</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>S om järnvägen, Vg</t>
+          <t>S om järnvägen - 11, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431889.3909100805</v>
+        <v>431937</v>
       </c>
       <c r="R4" t="n">
-        <v>6419670.266848063</v>
+        <v>6419626</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1014,19 +988,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,6 +1002,16 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1054,66 +1028,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111482936</v>
+        <v>111483300</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>S om järnvägen - 4, Vg</t>
+          <t>S om järnvägen - 12, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432073.5656663703</v>
+        <v>431888</v>
       </c>
       <c r="R5" t="n">
-        <v>6419668.734013095</v>
+        <v>6419625</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1143,19 +1099,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,6 +1113,26 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1183,66 +1149,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111482980</v>
+        <v>111483381</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S om järnvägen - 6, Vg</t>
+          <t>S om järnvägen - 14, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432048.2263952638</v>
+        <v>431754</v>
       </c>
       <c r="R6" t="n">
-        <v>6419681.385014677</v>
+        <v>6419729</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1272,19 +1220,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,6 +1234,26 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1312,69 +1270,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111482955</v>
+        <v>111661840</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S om järnvägen - 5, Vg</t>
+          <t>Stråkens strandskogar, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432064.1298546481</v>
+        <v>431769</v>
       </c>
       <c r="R7" t="n">
-        <v>6419677.395781181</v>
+        <v>6419728</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1398,22 +1338,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,30 +1356,40 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Johannes Glännman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Johannes Glännman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111483140</v>
+        <v>111483107</v>
       </c>
       <c r="B8" t="n">
-        <v>73683</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,21 +1397,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>306</v>
+        <v>6439</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1480,14 +1420,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S om järnvägen - 9, Vg</t>
+          <t>S om järnvägen - 8, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431942.9372677525</v>
+        <v>431947</v>
       </c>
       <c r="R8" t="n">
-        <v>6419625.784949708</v>
+        <v>6419623</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1517,19 +1457,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1577,56 +1507,64 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111483105</v>
+        <v>61235525</v>
       </c>
       <c r="B9" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>100070</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>S om järnvägen - 8, Vg</t>
+          <t>Mullsjö, lokal 19A, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431947.1499479365</v>
+        <v>431609</v>
       </c>
       <c r="R9" t="n">
-        <v>6419623.056550305</v>
+        <v>6419834</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,22 +1588,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2014-05-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2014-05-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,54 +1612,37 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Läge: Väster om Mullsjö, vid järnvägsbron över sjön Stråken. Beskrivning: Lokalen är ca 20*200 m och består av båda sidor om järnvägen vid östra sidan av Stråken, samt östra sidan av grusvägen som går fram till lokalen</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Anna Isaksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ogun Caglayan Turkay</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av sandödla i Jönköpings län 2014</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111491635</v>
+        <v>111396045</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1669,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1765,14 +1686,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>S om järnvägen - 21, Vg</t>
+          <t>S om järnvägen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431859.6228004749</v>
+        <v>431890</v>
       </c>
       <c r="R10" t="n">
-        <v>6419672.898494411</v>
+        <v>6419671</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1802,19 +1723,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1842,53 +1753,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111483381</v>
+        <v>111396053</v>
       </c>
       <c r="B11" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>S om järnvägen - 14, Vg</t>
+          <t>S om järnvägen - 2, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431754.10213514</v>
+        <v>432084</v>
       </c>
       <c r="R11" t="n">
-        <v>6419728.893211351</v>
+        <v>6419677</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1918,19 +1833,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1942,26 +1847,6 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1978,15 +1863,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111490843</v>
+        <v>111396060</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2013,31 +1893,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>S om järnvägen - 17, Vg</t>
+          <t>S om järnvägen - 3, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431803.2980747336</v>
+        <v>432076</v>
       </c>
       <c r="R12" t="n">
-        <v>6419679.170503675</v>
+        <v>6419661</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2067,19 +1943,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2107,15 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111483462</v>
+        <v>111482936</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2142,7 +2003,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2159,14 +2020,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>S om järnvägen - 16, Vg</t>
+          <t>S om järnvägen - 4, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431654.0242198514</v>
+        <v>432073</v>
       </c>
       <c r="R13" t="n">
-        <v>6419791.70470859</v>
+        <v>6419668</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2196,19 +2057,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2236,15 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111491187</v>
+        <v>111482955</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2271,7 +2117,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2288,14 +2134,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>S om järnvägen - 18, Vg</t>
+          <t>S om järnvägen - 5, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431829.514510141</v>
+        <v>432064</v>
       </c>
       <c r="R14" t="n">
-        <v>6419749.394753682</v>
+        <v>6419678</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2325,19 +2171,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2365,53 +2201,61 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111483197</v>
+        <v>111482980</v>
       </c>
       <c r="B15" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>S om järnvägen - 11, Vg</t>
+          <t>S om järnvägen - 6, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431937.082796899</v>
+        <v>432048</v>
       </c>
       <c r="R15" t="n">
-        <v>6419625.884406033</v>
+        <v>6419681</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2441,19 +2285,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2465,16 +2299,6 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2491,53 +2315,61 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111483107</v>
+        <v>111483037</v>
       </c>
       <c r="B16" t="n">
-        <v>73681</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>S om järnvägen - 8, Vg</t>
+          <t>S om järnvägen - 7, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431947.1499479365</v>
+        <v>432060</v>
       </c>
       <c r="R16" t="n">
-        <v>6419623.056550305</v>
+        <v>6419660</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2567,19 +2399,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2591,26 +2413,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2627,15 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111483037</v>
+        <v>111483437</v>
       </c>
       <c r="B17" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2662,7 +2459,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2679,14 +2476,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>S om järnvägen - 7, Vg</t>
+          <t>S om järnvägen - 15, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432060.6482816387</v>
+        <v>431797</v>
       </c>
       <c r="R17" t="n">
-        <v>6419660.45125766</v>
+        <v>6419681</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2716,19 +2513,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2756,15 +2543,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111483437</v>
+        <v>111483462</v>
       </c>
       <c r="B18" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2791,7 +2573,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2808,14 +2590,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>S om järnvägen - 15, Vg</t>
+          <t>S om järnvägen - 16, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431797.479853621</v>
+        <v>431654</v>
       </c>
       <c r="R18" t="n">
-        <v>6419681.394993878</v>
+        <v>6419791</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2845,19 +2627,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2885,53 +2657,61 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111483300</v>
+        <v>111490843</v>
       </c>
       <c r="B19" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>S om järnvägen - 12, Vg</t>
+          <t>S om järnvägen - 17, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431888.091041417</v>
+        <v>431804</v>
       </c>
       <c r="R19" t="n">
-        <v>6419625.122914318</v>
+        <v>6419679</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2961,19 +2741,9 @@
           <t>2023-08-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-08-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2985,26 +2755,6 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3021,56 +2771,64 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111661840</v>
+        <v>111491187</v>
       </c>
       <c r="B20" t="n">
-        <v>89793</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stråkens strandskogar, Vg</t>
+          <t>S om järnvägen - 18, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431769</v>
+        <v>431830</v>
       </c>
       <c r="R20" t="n">
-        <v>6419728</v>
+        <v>6419750</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3094,12 +2852,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3112,45 +2870,25 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111661831</v>
+        <v>111491327</v>
       </c>
       <c r="B21" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3175,20 +2913,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stråkens strandskogar, Vg</t>
+          <t>S om järnvägen - 18, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432080</v>
+        <v>431957</v>
       </c>
       <c r="R21" t="n">
-        <v>6419663</v>
+        <v>6419713</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3212,12 +2966,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3226,33 +2980,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111661838</v>
+        <v>111491535</v>
       </c>
       <c r="B22" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3277,20 +3027,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stråkens strandskogar, Vg</t>
+          <t>S om järnvägen - 20, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431799</v>
+        <v>431974</v>
       </c>
       <c r="R22" t="n">
-        <v>6419691</v>
+        <v>6419730</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3314,12 +3076,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3328,33 +3090,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johannes Glännman</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111661832</v>
+        <v>111491635</v>
       </c>
       <c r="B23" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3379,20 +3137,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stråkens strandskogar, Vg</t>
+          <t>S om järnvägen - 21, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432076</v>
+        <v>431859</v>
       </c>
       <c r="R23" t="n">
-        <v>6419683</v>
+        <v>6419673</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3416,12 +3190,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3430,21 +3204,507 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna Pielach</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>111661831</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stråkens strandskogar, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>432081</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6419662</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nykyrka</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Johannes Glännman</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Johannes Glännman</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>111661832</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stråkens strandskogar, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>432076</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6419683</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nykyrka</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johannes Glännman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johannes Glännman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>111661834</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stråkens strandskogar, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>432067</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6419711</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nykyrka</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Johannes Glännman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Johannes Glännman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>111661836</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stråkens strandskogar, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>431877</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6419686</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nykyrka</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Johannes Glännman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Johannes Glännman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>111661838</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stråkens strandskogar, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>431799</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6419691</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nykyrka</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johannes Glännman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johannes Glännman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13663-2023 artfynd.xlsx
+++ b/artfynd/A 13663-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483105</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483197</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483300</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483381</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1383,6 +1413,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111661840</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1504,6 +1539,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483107</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1636,6 +1676,11 @@
           <t>Inventering av sandödla i Jönköpings län 2014</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61235525</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1750,6 +1795,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111396045</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1860,6 +1910,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111396053</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1970,6 +2025,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111396060</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2084,6 +2144,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111482936</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2198,6 +2263,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111482955</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2312,6 +2382,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111482980</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2426,6 +2501,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483037</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2540,6 +2620,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483437</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2654,6 +2739,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483462</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2768,6 +2858,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111490843</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2882,6 +2977,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491187</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2996,6 +3096,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491327</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3106,6 +3211,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491535</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3220,6 +3330,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111491635</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3317,6 +3432,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111661831</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3414,6 +3534,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111661832</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3511,6 +3636,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111661834</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3608,6 +3738,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111661836</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3705,8 +3840,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111661838</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>